--- a/www/download/IND.gdp.s.mv.rpPE.xlsx
+++ b/www/download/IND.gdp.s.mv.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>24931.172</t>
+          <t>24931172398.943</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24845.95</t>
+          <t>24845950026.7115</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25547.92</t>
+          <t>25547919682.4449</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27644.666</t>
+          <t>27644665892.3313</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>28975.24</t>
+          <t>28975239803.6837</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>31122.763</t>
+          <t>31122763478.9434</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>31529.621</t>
+          <t>31529621340.3706</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32107.017</t>
+          <t>32107017243.4628</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>30258.866</t>
+          <t>30258865797.062</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>31868.322</t>
+          <t>31868322478.1802</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>32269.641</t>
+          <t>32269640918.7014</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>32402.135</t>
+          <t>32402134668.943</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>31217.012</t>
+          <t>31217012110.4157</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>32032.182</t>
+          <t>32032181978.4291</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>33928.04</t>
+          <t>33928040308.2064</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13059.666</t>
+          <t>13059665765.6407</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12932.389</t>
+          <t>12932388768.6081</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13221.989</t>
+          <t>13221988919.3899</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14053.212</t>
+          <t>14053211728.7934</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14615.483</t>
+          <t>14615482945.9755</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15341.7</t>
+          <t>15341700361.1875</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15658.554</t>
+          <t>15658553552.2183</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15493.199</t>
+          <t>15493198996.4937</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>13825.526</t>
+          <t>13825526186.6256</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>15388.967</t>
+          <t>15388967024.8401</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>14745.024</t>
+          <t>14745024435.8472</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>14256.155</t>
+          <t>14256154974.1692</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>13384.07</t>
+          <t>13384069972.0352</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>12991999829.1406</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>12477.262</t>
+          <t>12477262186.7234</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8950.125</t>
+          <t>8950125108.89151</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8833.509</t>
+          <t>8833508926.92818</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9021.839</t>
+          <t>9021839023.79133</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9616.457</t>
+          <t>9616457330.98277</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9947.009</t>
+          <t>9947008548.53844</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10684.075</t>
+          <t>10684075131.4926</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10836.137</t>
+          <t>10836136804.0425</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10575.832</t>
+          <t>10575831545.5741</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>9615.31</t>
+          <t>9615309978.62098</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10327.591</t>
+          <t>10327591412.3265</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10160.822</t>
+          <t>10160822208.5599</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10049.041</t>
+          <t>10049040538.8444</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>9601.67</t>
+          <t>9601670440.34281</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>9647.583</t>
+          <t>9647582836.4123</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>9558.451</t>
+          <t>9558451401.92132</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8462.855</t>
+          <t>8462855038.91892</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8494.293</t>
+          <t>8494293483.13036</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8064.141</t>
+          <t>8064141172.99384</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7565.45</t>
+          <t>7565450241.13256</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7382.997</t>
+          <t>7382996904.33266</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7112.329</t>
+          <t>7112329091.29758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6853.303</t>
+          <t>6853302568.17376</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6693.397</t>
+          <t>6693396641.12012</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6586.465</t>
+          <t>6586464773.08358</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>7286.487</t>
+          <t>7286486745.65539</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>7346.891</t>
+          <t>7346891233.81137</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7461.557</t>
+          <t>7461556736.10504</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>7361.44</t>
+          <t>7361440105.05063</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>7216.81</t>
+          <t>7216809950.00969</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>7220.786</t>
+          <t>7220786117.00753</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>178424.625</t>
+          <t>178424625442.025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>174913.684</t>
+          <t>174913683636.339</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>182308.753</t>
+          <t>182308752512.481</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>190456.367</t>
+          <t>190456366591.858</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>204465.247</t>
+          <t>204465247264.515</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>219924.87</t>
+          <t>219924869911.934</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>224161.463</t>
+          <t>224161463022.478</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>230044.315</t>
+          <t>230044315232.367</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>220560.279</t>
+          <t>220560279135.946</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>245626.614</t>
+          <t>245626613740.203</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>250680.169</t>
+          <t>250680169227.314</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>256894.344</t>
+          <t>256894344237.194</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>258022.22</t>
+          <t>258022219614.507</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>262100.529</t>
+          <t>262100529094.321</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>266787.538</t>
+          <t>266787537885.272</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>49372.088</t>
+          <t>49372088025.6858</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>49069.547</t>
+          <t>49069546856.5704</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>50386.59</t>
+          <t>50386590345.6236</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53649.798</t>
+          <t>53649798184.3888</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>55512.38</t>
+          <t>55512379862.4522</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>59370.859</t>
+          <t>59370859484.6487</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>58739.315</t>
+          <t>58739315194.854</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>58073.634</t>
+          <t>58073633821.8976</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>53199.12</t>
+          <t>53199120227.4232</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>57473.402</t>
+          <t>57473401628.7618</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>56954.085</t>
+          <t>56954084926.0083</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>56458.515</t>
+          <t>56458514845.5237</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>53720.302</t>
+          <t>53720302443.7431</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>51277.65</t>
+          <t>51277649729.9031</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>50410.775</t>
+          <t>50410775135.666</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1556925.183</t>
+          <t>1556925183178.48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1574294.326</t>
+          <t>1574294325984.67</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1606111.409</t>
+          <t>1606111409171.48</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1656495.728</t>
+          <t>1656495728241.19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1711762.079</t>
+          <t>1711762079414.12</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1778694.119</t>
+          <t>1778694118807.88</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1821264.232</t>
+          <t>1821264231511.25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1847242.456</t>
+          <t>1847242456249.77</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1793264.858</t>
+          <t>1793264857953.38</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1902931.038</t>
+          <t>1902931038216.09</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1940797.279</t>
+          <t>1940797279015.86</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2032168.706</t>
+          <t>2032168705564.69</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1999045.63</t>
+          <t>1999045629927.12</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2038451.688</t>
+          <t>2038451687669.34</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2067314.247</t>
+          <t>2067314247142.77</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1041.998</t>
+          <t>1041997520.93818</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1021.044</t>
+          <t>1021044338.09878</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1000.045</t>
+          <t>1000045247.41479</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1019.057</t>
+          <t>1019056626.78826</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1040.734</t>
+          <t>1040734261.82765</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1114.238</t>
+          <t>1114237619.09915</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1146.978</t>
+          <t>1146977766.10291</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1144.392</t>
+          <t>1144392339.37645</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1071.983</t>
+          <t>1071983320.00049</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1113.225</t>
+          <t>1113225252.04762</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1101.804</t>
+          <t>1101804241.44741</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1099.722</t>
+          <t>1099721648.53697</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1110.986</t>
+          <t>1110986466.17874</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1056.494</t>
+          <t>1056494488.23706</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1061.376</t>
+          <t>1061375713.43295</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>25368.065</t>
+          <t>25368065024.4935</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>25054.881</t>
+          <t>25054881212.8234</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24981.371</t>
+          <t>24981370923.8904</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25740.518</t>
+          <t>25740518101.2677</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>25458.569</t>
+          <t>25458568942.5114</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>26188.17</t>
+          <t>26188169781.4576</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25247.073</t>
+          <t>25247073326.7017</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>24519.968</t>
+          <t>24519968238.4232</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>21784.542</t>
+          <t>21784542118.8611</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>23294.005</t>
+          <t>23294004809.7037</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>23334.833</t>
+          <t>23334832995.5037</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>23114.458</t>
+          <t>23114458207.5785</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>21880.898</t>
+          <t>21880897512.1471</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>21398.98</t>
+          <t>21398979638.1386</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>20623.331</t>
+          <t>20623330825.1649</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>139707.897</t>
+          <t>139707896661.57</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>132049.177</t>
+          <t>132049177264.084</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>130479.746</t>
+          <t>130479746001.07</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>142637.795</t>
+          <t>142637795409.519</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>143845.543</t>
+          <t>143845542694.81</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>147919.66</t>
+          <t>147919660496.804</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>145895.792</t>
+          <t>145895791847.453</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>141669.685</t>
+          <t>141669684691.592</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>130135.587</t>
+          <t>130135587259.658</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>138998.127</t>
+          <t>138998127100.939</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>131258.755</t>
+          <t>131258755367.96</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>125970.948</t>
+          <t>125970948407.574</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>119042.671</t>
+          <t>119042671235.684</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>113978.826</t>
+          <t>113978825585.364</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>113623.134</t>
+          <t>113623134187.113</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10068.69</t>
+          <t>10068689817.9808</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9917.262</t>
+          <t>9917261606.48113</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10317.686</t>
+          <t>10317686036.7268</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11257.954</t>
+          <t>11257953675.0811</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11743.225</t>
+          <t>11743225258.6914</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12367.628</t>
+          <t>12367628446.0481</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12468.426</t>
+          <t>12468426320.2055</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12322.308</t>
+          <t>12322308150.8646</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11153.15</t>
+          <t>11153149887.3275</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11688.829</t>
+          <t>11688828600.8258</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>11616.572</t>
+          <t>11616572017.1955</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>11536.247</t>
+          <t>11536246602.3375</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10145.945</t>
+          <t>10145945159.2872</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>10089.798</t>
+          <t>10089798376.9246</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>9914.553</t>
+          <t>9914553180.33491</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>38505.544</t>
+          <t>38505544223.9853</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>40439.698</t>
+          <t>40439697880.9752</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>42796.362</t>
+          <t>42796362413.5974</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47989.662</t>
+          <t>47989661938.825</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>51859.126</t>
+          <t>51859126033.8631</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>58294.448</t>
+          <t>58294448473.6002</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>60327.484</t>
+          <t>60327483754.3451</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>62140.86</t>
+          <t>62140860343.831</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>58606.7</t>
+          <t>58606700110.0555</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>63166.132</t>
+          <t>63166131636.3164</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>65315.049</t>
+          <t>65315049236.9161</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>66160.566</t>
+          <t>66160566466.0866</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>63218.684</t>
+          <t>63218683745.4767</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>59118.819</t>
+          <t>59118819388.3548</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>55901.689</t>
+          <t>55901689296.9971</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3960.309</t>
+          <t>3960308734.1812</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3732.367</t>
+          <t>3732367329.76395</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3660.429</t>
+          <t>3660428646.09747</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3673.523</t>
+          <t>3673522778.16707</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3445.5</t>
+          <t>3445500231.90435</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3509.555</t>
+          <t>3509555091.48769</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3619.364</t>
+          <t>3619364068.69958</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3549.595</t>
+          <t>3549594557.65591</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3308.698</t>
+          <t>3308698067.67965</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3639.8</t>
+          <t>3639800002.73002</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3575.918</t>
+          <t>3575917797.31143</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3663.784</t>
+          <t>3663784454.62748</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>3463.549</t>
+          <t>3463548983.50534</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3211.196</t>
+          <t>3211195905.26364</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2816.741</t>
+          <t>2816740645.4184</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10079.733</t>
+          <t>10079733141.4119</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10062.914</t>
+          <t>10062914154.441</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10512.782</t>
+          <t>10512781531.2676</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>11240.622</t>
+          <t>11240622347.7575</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11762.826</t>
+          <t>11762826316.7695</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>12260.868</t>
+          <t>12260867502.3191</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12384.219</t>
+          <t>12384218817.6179</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12271.758</t>
+          <t>12271758064.5264</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11002.038</t>
+          <t>11002038155.3517</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11778.792</t>
+          <t>11778792433.5554</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>11596.188</t>
+          <t>11596188119.9773</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>11473.393</t>
+          <t>11473393215.3287</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>10943.021</t>
+          <t>10943020653.3044</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>10502.126</t>
+          <t>10502125679.9096</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>10340.918</t>
+          <t>10340918100.9592</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>69999.547</t>
+          <t>69999546965.1131</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>69885.385</t>
+          <t>69885384719.9218</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>70938.646</t>
+          <t>70938646371.741</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>75821.39</t>
+          <t>75821390252.2184</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>79170.164</t>
+          <t>79170163616.3521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>81770.94</t>
+          <t>81770939653.2675</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>82643.068</t>
+          <t>82643067840.9537</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>80193.641</t>
+          <t>80193640645.5389</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>72405.612</t>
+          <t>72405612402.8048</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>77255.376</t>
+          <t>77255376393.7468</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>76466.921</t>
+          <t>76466921465.8622</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>75122.724</t>
+          <t>75122724234.4216</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>73576.322</t>
+          <t>73576321625.9399</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>71650.018</t>
+          <t>71650017564.4913</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>71029.312</t>
+          <t>71029312094.233</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>88837.129</t>
+          <t>88837129137.372</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>87986.287</t>
+          <t>87986286516.3065</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>92797.927</t>
+          <t>92797926609.8677</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>100674.914</t>
+          <t>100674914025.089</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>104936.818</t>
+          <t>104936818354.264</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>111047.135</t>
+          <t>111047134587.955</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>111404.532</t>
+          <t>111404531513.795</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>111493.082</t>
+          <t>111493082056.012</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>100773.866</t>
+          <t>100773865700.543</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>105522.128</t>
+          <t>105522128188.607</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>104210.77</t>
+          <t>104210770353.512</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>102427.299</t>
+          <t>102427299431.443</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>96108.517</t>
+          <t>96108517381.0756</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>90437.728</t>
+          <t>90437728052.3026</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>91418.97</t>
+          <t>91418970188.5338</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12451.177</t>
+          <t>12451177208.7034</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12310.361</t>
+          <t>12310361349.9203</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12248.765</t>
+          <t>12248765251.1449</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13609.101</t>
+          <t>13609100755.5146</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14278.12</t>
+          <t>14278120339.6252</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14876.726</t>
+          <t>14876725719.0423</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>14794.196</t>
+          <t>14794195711.7728</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14793.634</t>
+          <t>14793633552.0254</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>13566.527</t>
+          <t>13566527466.5995</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>15184.056</t>
+          <t>15184055674.6428</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>14673.224</t>
+          <t>14673223775.0162</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>15395.542</t>
+          <t>15395541923.3675</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>14724.89</t>
+          <t>14724890329.8124</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>13905.749</t>
+          <t>13905749063.5335</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>14150.815</t>
+          <t>14150815407.4427</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20397.063</t>
+          <t>20397062574.2543</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19799.346</t>
+          <t>19799345909.8454</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19817.167</t>
+          <t>19817166907.8402</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>21259.257</t>
+          <t>21259257327.356</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22822.768</t>
+          <t>22822768208.1445</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23158.521</t>
+          <t>23158521120.158</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>22442.239</t>
+          <t>22442238814.9532</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>22275.994</t>
+          <t>22275994294.9742</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>20210.736</t>
+          <t>20210735819.5944</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>21465.242</t>
+          <t>21465241725.9532</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>20457.17</t>
+          <t>20457170147.2405</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>20165.416</t>
+          <t>20165416140.1115</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>18747.822</t>
+          <t>18747822142.6306</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>17047.873</t>
+          <t>17047873143.8158</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>17384.93</t>
+          <t>17384929760.002</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>141539.627</t>
+          <t>141539627058.49</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>145843.082</t>
+          <t>145843081657.67</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>145611.139</t>
+          <t>145611138951.918</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>156516.804</t>
+          <t>156516804089.146</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>172600.62</t>
+          <t>172600620418.06</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>189867.396</t>
+          <t>189867395624.538</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>190643.727</t>
+          <t>190643726609.771</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>196794.454</t>
+          <t>196794454000.953</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>191580.349</t>
+          <t>191580348601.285</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>203942.313</t>
+          <t>203942313104.014</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>179633.208</t>
+          <t>179633208340.673</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>168446.961</t>
+          <t>168446960755.248</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>166664.956</t>
+          <t>166664956354.852</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>162731.794</t>
+          <t>162731794249.439</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>166962.187</t>
+          <t>166962186580.14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1341972.567</t>
+          <t>1341972567225.11</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1384879.535</t>
+          <t>1384879535059.03</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1420406.074</t>
+          <t>1420406073977.77</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1493139.839</t>
+          <t>1493139838813.7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1516677.69</t>
+          <t>1516677690146.71</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1663754.86</t>
+          <t>1663754860413.74</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1768994.808</t>
+          <t>1768994807670.4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1763814.127</t>
+          <t>1763814126839.49</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1761091.437</t>
+          <t>1761091437012.11</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1903826.179</t>
+          <t>1903826178785.05</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1925866.913</t>
+          <t>1925866913090.1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1904057.09</t>
+          <t>1904057090286.2</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1780827.822</t>
+          <t>1780827822009.07</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1733815.962</t>
+          <t>1733815962252.8</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1747265.704</t>
+          <t>1747265704387.91</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5553.709</t>
+          <t>5553708669.98142</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5861.572</t>
+          <t>5861572107.8533</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6087.153</t>
+          <t>6087153338.15704</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6835.493</t>
+          <t>6835493487.25106</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>7459.848</t>
+          <t>7459847931.67516</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8088.594</t>
+          <t>8088593659.99475</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8323.805</t>
+          <t>8323805137.3529</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8483.758</t>
+          <t>8483757932.23256</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8003.873</t>
+          <t>8003873202.40203</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8790.402</t>
+          <t>8790402221.09613</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>9111.274</t>
+          <t>9111274422.30145</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>9458.579</t>
+          <t>9458579312.34756</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>9157.064</t>
+          <t>9157064444.37362</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>9097.693</t>
+          <t>9097693132.64385</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>8789.482</t>
+          <t>8789481645.52705</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52544.54</t>
+          <t>52544539523.7314</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>53074.397</t>
+          <t>53074396827.6688</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>54842.943</t>
+          <t>54842942566.5294</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>59943.656</t>
+          <t>59943655575.7592</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>62676.338</t>
+          <t>62676337802.8511</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>65279.544</t>
+          <t>65279544010.1646</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>63964.157</t>
+          <t>63964156739.5311</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>63807.285</t>
+          <t>63807284909.0523</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>60302.701</t>
+          <t>60302701098.171</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>63867.42</t>
+          <t>63867419880.6265</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>64764.298</t>
+          <t>64764298108.6569</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>65304.001</t>
+          <t>65304001180.1629</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>62868.372</t>
+          <t>62868371981.3215</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>61590.351</t>
+          <t>61590350645.3175</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>59623.296</t>
+          <t>59623296257.4948</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>278938.394</t>
+          <t>278938393622.43</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>276209.145</t>
+          <t>276209145397.969</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>278882.13</t>
+          <t>278882129750.683</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>286906.446</t>
+          <t>286906446307.961</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>289365.512</t>
+          <t>289365512099.909</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>302975.529</t>
+          <t>302975528609.354</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>301505.619</t>
+          <t>301505619064.406</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>290179.36</t>
+          <t>290179360349.808</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>264525.087</t>
+          <t>264525087493.508</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>278273.59</t>
+          <t>278273589784.634</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>267645.85</t>
+          <t>267645850346.53</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>261493.883</t>
+          <t>261493883438.054</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>244324.5</t>
+          <t>244324500023.567</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>223985.677</t>
+          <t>223985677175.946</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>208162.228</t>
+          <t>208162228255.356</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>139636.705</t>
+          <t>139636705369.591</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>137424.44</t>
+          <t>137424440287.068</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>139795.718</t>
+          <t>139795717669.968</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>142794.732</t>
+          <t>142794731729.732</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>150385.394</t>
+          <t>150385394486.781</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>165400.567</t>
+          <t>165400567407.159</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>167046.954</t>
+          <t>167046953704.707</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>168826.775</t>
+          <t>168826775369.341</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>155974.796</t>
+          <t>155974796304.074</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>171721.991</t>
+          <t>171721991483.136</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>160776.292</t>
+          <t>160776291818.06</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>156185.619</t>
+          <t>156185618779.957</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>141459.781</t>
+          <t>141459781084.514</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>134408.389</t>
+          <t>134408389087.494</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>134893.339</t>
+          <t>134893339466.303</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8182.721</t>
+          <t>8182720693.47498</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7987.288</t>
+          <t>7987287729.2084</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7763.567</t>
+          <t>7763567420.37812</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8350.744</t>
+          <t>8350744245.89615</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7969.033</t>
+          <t>7969032813.48135</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8658.09</t>
+          <t>8658090142.2502</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8257.677</t>
+          <t>8257677257.4662</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8049.806</t>
+          <t>8049806285.33834</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7497.865</t>
+          <t>7497865402.92593</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7941.568</t>
+          <t>7941568104.49453</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8328.687</t>
+          <t>8328687400.50609</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7989.524</t>
+          <t>7989524157.24004</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>7919.033</t>
+          <t>7919032637.78597</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>7604.557</t>
+          <t>7604556585.09226</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>7046.024</t>
+          <t>7046024204.02494</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>544.599</t>
+          <t>544598619.965882</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>541.099</t>
+          <t>541098564.16945</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>570.1</t>
+          <t>570099877.881843</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>629.775</t>
+          <t>629775167.838513</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>657.784</t>
+          <t>657783592.33772</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>721.404</t>
+          <t>721403758.371099</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>741.407</t>
+          <t>741407477.626674</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>755.407</t>
+          <t>755407026.384801</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>651.382</t>
+          <t>651381971.092161</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>813.353</t>
+          <t>813352893.852519</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>823.097</t>
+          <t>823096657.22782</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>792.47</t>
+          <t>792470034.477017</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>778.771</t>
+          <t>778770973.681525</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>795.706</t>
+          <t>795705601.473041</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>932.523</t>
+          <t>932523259.899665</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4409.176</t>
+          <t>4409176429.91266</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4263.37</t>
+          <t>4263369620.57123</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4257.925</t>
+          <t>4257925255.22466</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4307.887</t>
+          <t>4307887301.79997</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4141.193</t>
+          <t>4141193345.50213</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4009.774</t>
+          <t>4009774365.60634</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3888.262</t>
+          <t>3888261529.25562</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3733.542</t>
+          <t>3733542085.01387</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3413.976</t>
+          <t>3413976054.03424</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3677.913</t>
+          <t>3677913367.31206</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3543.839</t>
+          <t>3543839277.59957</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3616.782</t>
+          <t>3616782317.2891</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3451.865</t>
+          <t>3451864741.79681</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3266.212</t>
+          <t>3266211994.87538</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2533.771</t>
+          <t>2533771178.39263</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>123970.852</t>
+          <t>123970851844.056</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>128224.535</t>
+          <t>128224534541.491</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>134805.632</t>
+          <t>134805631839.345</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>144584.412</t>
+          <t>144584412421.456</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>151597.847</t>
+          <t>151597847099.562</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>160976.989</t>
+          <t>160976989470.537</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>164165.799</t>
+          <t>164165798652.887</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>163744.535</t>
+          <t>163744535265.359</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>154362.639</t>
+          <t>154362638943.898</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>170732.417</t>
+          <t>170732416682.891</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>175743.148</t>
+          <t>175743148357.584</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>171719.922</t>
+          <t>171719921502.388</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>163090.666</t>
+          <t>163090665993.722</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>167734.614</t>
+          <t>167734614121.841</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>165223.781</t>
+          <t>165223781494.59</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>327.788</t>
+          <t>327788296.770841</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>322.392</t>
+          <t>322392117.655215</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>312.542</t>
+          <t>312541635.526216</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>316.741</t>
+          <t>316740582.810686</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>328.28</t>
+          <t>328280124.889305</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>344.337</t>
+          <t>344337058.000144</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>300.668</t>
+          <t>300667634.55923</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>347.635</t>
+          <t>347634791.372373</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>320.035</t>
+          <t>320035309.27817</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>362.139</t>
+          <t>362139087.215833</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>346.55</t>
+          <t>346549920.00284</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>342.769</t>
+          <t>342769340.774915</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>321.707</t>
+          <t>321707070.91782</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>308.102</t>
+          <t>308102378.358443</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>318.482</t>
+          <t>318482155.64948</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>18669.494</t>
+          <t>18669493680.016</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>18920.567</t>
+          <t>18920566701.6263</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19760.372</t>
+          <t>19760371722.7344</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>21211.291</t>
+          <t>21211291307.5816</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22885.921</t>
+          <t>22885921048.0205</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>22544.236</t>
+          <t>22544236190.4848</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23118.761</t>
+          <t>23118761384.5999</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>23658.303</t>
+          <t>23658303308.6921</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>22480.704</t>
+          <t>22480704337.7082</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>24312.821</t>
+          <t>24312821236.8343</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>23714.207</t>
+          <t>23714206928.8787</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>23235.821</t>
+          <t>23235821317.004</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>22001.488</t>
+          <t>22001488100.4723</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>21350.354</t>
+          <t>21350353632.576</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>21497.682</t>
+          <t>21497682203.6311</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>74656.975</t>
+          <t>74656974699.0005</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>73729.677</t>
+          <t>73729676646.5518</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>74523.417</t>
+          <t>74523416623.7368</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>78071.768</t>
+          <t>78071768297.3649</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>77118.202</t>
+          <t>77118201534.9655</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>77716.712</t>
+          <t>77716712143.7228</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>70970.166</t>
+          <t>70970166391.2177</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>67678.978</t>
+          <t>67678978292.3362</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>62688.101</t>
+          <t>62688101276.2443</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>67697.525</t>
+          <t>67697524825.8621</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>68175.553</t>
+          <t>68175552739.4301</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>68747.244</t>
+          <t>68747244233.8625</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>66008.509</t>
+          <t>66008508841.3377</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>65580.558</t>
+          <t>65580558244.4238</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>65393.542</t>
+          <t>65393542208.5763</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9532.104</t>
+          <t>9532104010.05766</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9451.895</t>
+          <t>9451895257.45487</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>9205.803</t>
+          <t>9205802962.43903</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>9278.371</t>
+          <t>9278371017.16703</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>9683.579</t>
+          <t>9683579005.25829</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>10215.834</t>
+          <t>10215833504.629</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10349.016</t>
+          <t>10349016225.4391</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>10262.443</t>
+          <t>10262442850.6247</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>9755.536</t>
+          <t>9755536268.35281</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>10578.22</t>
+          <t>10578220428.5806</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10394.592</t>
+          <t>10394591710.9577</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>10715.459</t>
+          <t>10715459066.2727</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>10382.214</t>
+          <t>10382213690.9868</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>10144.956</t>
+          <t>10144955694.5727</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>10256.324</t>
+          <t>10256323580.691</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>24576.388</t>
+          <t>24576388100.5527</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>24506.049</t>
+          <t>24506048837.2106</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>22509.642</t>
+          <t>22509642277.5957</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>21831.028</t>
+          <t>21831027847.5994</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>25357.485</t>
+          <t>25357484630.7332</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>25493.381</t>
+          <t>25493381152.9765</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>25456.006</t>
+          <t>25456006155.2087</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>24040.968</t>
+          <t>24040967749.4967</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>23265.42</t>
+          <t>23265420212.9555</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>23757.591</t>
+          <t>23757591325.361</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>23435.562</t>
+          <t>23435562477.6562</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>23467.174</t>
+          <t>23467173653.9063</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>22768.07</t>
+          <t>22768069596.9621</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>22689.274</t>
+          <t>22689274379.6064</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>22952.407</t>
+          <t>22952406923.7938</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>436946.446</t>
+          <t>436946446291.871</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>415478.922</t>
+          <t>415478922343.414</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>398331.132</t>
+          <t>398331132362.087</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>397750.215</t>
+          <t>397750215020.591</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>408254.988</t>
+          <t>408254987715.936</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>429349.784</t>
+          <t>429349784326.5</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>430461.746</t>
+          <t>430461745863.206</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>424040.774</t>
+          <t>424040773690.563</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>385879.583</t>
+          <t>385879583108.403</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>408673.417</t>
+          <t>408673417262.61</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>398879.388</t>
+          <t>398879387858.787</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>388515.139</t>
+          <t>388515138964.496</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>365716.564</t>
+          <t>365716564081.767</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>346895.726</t>
+          <t>346895725701.889</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>336391.901</t>
+          <t>336391900517.481</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>10644.069</t>
+          <t>10644069142.508</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10042.866</t>
+          <t>10042865861.8409</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>9940.857</t>
+          <t>9940856528.87513</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>10131.419</t>
+          <t>10131418670.5912</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>9939.892</t>
+          <t>9939891670.69165</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>10083.29</t>
+          <t>10083290013.1518</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10003.035</t>
+          <t>10003035334.5717</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>9349.155</t>
+          <t>9349155060.83502</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8257.653</t>
+          <t>8257652771.0119</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>9013.785</t>
+          <t>9013785039.16185</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>8918.275</t>
+          <t>8918274599.92079</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>8596.393</t>
+          <t>8596392790.56777</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>8272.353</t>
+          <t>8272353242.42417</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>8216.207</t>
+          <t>8216206521.46146</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>7992.035</t>
+          <t>7992035355.85468</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4150.354</t>
+          <t>4150353702.35116</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3926.297</t>
+          <t>3926296882.47428</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3874.097</t>
+          <t>3874096602.01638</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4024.358</t>
+          <t>4024358170.44064</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4183.53</t>
+          <t>4183530396.32705</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4477.461</t>
+          <t>4477460972.10512</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4259.184</t>
+          <t>4259183599.56315</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4250.123</t>
+          <t>4250123106.57217</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>3962.85</t>
+          <t>3962849800.58885</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>4236.236</t>
+          <t>4236235845.6936</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>4174.382</t>
+          <t>4174381544.84335</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>4140.2</t>
+          <t>4140199616.07638</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>3961.329</t>
+          <t>3961328669.09762</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>3999.662</t>
+          <t>3999661835.50481</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>3957.884</t>
+          <t>3957883780.8451</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>16069.16</t>
+          <t>16069160380.278</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15776.939</t>
+          <t>15776939318.3753</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15803.807</t>
+          <t>15803807012.5755</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>16899.212</t>
+          <t>16899212108.1843</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>17835.814</t>
+          <t>17835814388.6526</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>20042.845</t>
+          <t>20042844537.9941</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20472.844</t>
+          <t>20472844010.1583</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>20165.992</t>
+          <t>20165991835.9378</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18124.593</t>
+          <t>18124592859.6186</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>19358.543</t>
+          <t>19358543491.0842</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>19059.269</t>
+          <t>19059268727.7993</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>18742.037</t>
+          <t>18742037242.314</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>18145.087</t>
+          <t>18145086532.1894</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>17603.791</t>
+          <t>17603791456.0744</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>17073.737</t>
+          <t>17073737274.294</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>49541.911</t>
+          <t>49541910879.9522</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>52266.732</t>
+          <t>52266732491.7082</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>53778.472</t>
+          <t>53778471996.0827</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>53880.075</t>
+          <t>53880074754.0414</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>54638.434</t>
+          <t>54638434021.3566</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>53944.722</t>
+          <t>53944721786.8563</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>54350.918</t>
+          <t>54350917644.6807</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>54603.686</t>
+          <t>54603685766.1651</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>52394.133</t>
+          <t>52394132578.2095</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>53508.023</t>
+          <t>53508022719.0912</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>56511.84</t>
+          <t>56511840215.8329</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>54870.347</t>
+          <t>54870346763.0767</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>51624.942</t>
+          <t>51624941784.2604</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>51489.053</t>
+          <t>51489053302.4594</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>50781.634</t>
+          <t>50781634347.3628</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>36374.633</t>
+          <t>36374632706.5526</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>36517.033</t>
+          <t>36517032570.5838</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>38616.057</t>
+          <t>38616056576.2768</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>41430.168</t>
+          <t>41430167556.2293</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>43476.459</t>
+          <t>43476458507.9509</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>46952.054</t>
+          <t>46952054436.7811</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>45051.33</t>
+          <t>45051330191.5908</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>45629.977</t>
+          <t>45629977245.9058</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>42772.181</t>
+          <t>42772180753.3439</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>46433.551</t>
+          <t>46433551069.527</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>47165.922</t>
+          <t>47165921986.7582</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>47084.415</t>
+          <t>47084414681.8811</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>45733.941</t>
+          <t>45733940900.6786</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>44704.138</t>
+          <t>44704137992.6722</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>44568.189</t>
+          <t>44568189188.35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>442117.937</t>
+          <t>442117936941.065</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>440203.219</t>
+          <t>440203219386.783</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>450990.336</t>
+          <t>450990336425.763</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>492290.67</t>
+          <t>492290670153.553</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>507157.927</t>
+          <t>507157927101.499</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>539863.426</t>
+          <t>539863425891.622</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>532461.943</t>
+          <t>532461942956.41</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>513687.436</t>
+          <t>513687435854.877</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>457882.9</t>
+          <t>457882900473.873</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>493768.597</t>
+          <t>493768596612.677</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>486133.958</t>
+          <t>486133957693.33</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>485546.29</t>
+          <t>485546290366.839</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>456834.325</t>
+          <t>456834325031.305</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>428835.872</t>
+          <t>428835872076.937</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>412753.856</t>
+          <t>412753855915.859</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3682488.408</t>
+          <t>3682488408276.7</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3747323.253</t>
+          <t>3747323252571.6</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3872447.989</t>
+          <t>3872447989075.92</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4116432.71</t>
+          <t>4116432709627.98</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4282654.045</t>
+          <t>4282654045361.5</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4694440.21</t>
+          <t>4694440209590.08</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4918545.297</t>
+          <t>4918545296517.85</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>5038017.752</t>
+          <t>5038017751561.45</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4885826.591</t>
+          <t>4885826591140.47</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>5399106.268</t>
+          <t>5399106268176.08</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>5434725.666</t>
+          <t>5434725665640.52</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>5547712.223</t>
+          <t>5547712222799.33</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>5380254.966</t>
+          <t>5380254966184.27</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>5410127.97</t>
+          <t>5410127969924.96</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>5598346.269</t>
+          <t>5598346268950.12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9163931.422</t>
+          <t>9163931422133.01</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9258416.723</t>
+          <t>9258416722745.6</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>9477330.469</t>
+          <t>9477330469218.35</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>9981963.286</t>
+          <t>9981963285702.94</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>10330069.644</t>
+          <t>10330069644247</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>11119959.644</t>
+          <t>11119959643825.2</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>11484749.122</t>
+          <t>11484749121528.4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>11590527.038</t>
+          <t>11590527037843.3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>11152344.251</t>
+          <t>11152344251334.2</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>12118401.996</t>
+          <t>12118401996492</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>12154432.887</t>
+          <t>12154432887348</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>12296600.895</t>
+          <t>12296600894896.7</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>11837883.974</t>
+          <t>11837883973819.6</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>11763092.666</t>
+          <t>11763092665962.3</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>11949679.149</t>
+          <t>11949679148709.3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
